--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -1,144 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nimeshikamadushani/Desktop/uni/semester 2/teammate-A/task-A3-eval-questions/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA2B80B-1063-A548-9A2D-A7AB38F2C5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>query</t>
-  </si>
-  <si>
-    <t>true_answer</t>
-  </si>
-  <si>
-    <t>How are inventories measured under IAS 2?</t>
-  </si>
-  <si>
-    <t>At the lower of cost and net realisable value (IAS 2, paragraph 9).</t>
-  </si>
-  <si>
-    <t>What is net realisable value according to IAS 2?</t>
-  </si>
-  <si>
-    <t>The estimated selling price in the ordinary course of business less the estimated costs of completion and the estimated costs necessary to make the sale (IAS 2, paragraph 6).</t>
-  </si>
-  <si>
-    <t>Which cost formulas does IAS 2 allow for inventories?</t>
-  </si>
-  <si>
-    <t>Specific identification for items not ordinarily interchangeable; otherwise FIFO (first-in, first-out) or weighted average cost. The same formula must be used for all inventories of similar nature and use (IAS 2, paragraphs 23-25).</t>
-  </si>
-  <si>
-    <t>Does IAS 2 permit the LIFO cost formula?</t>
-  </si>
-  <si>
-    <t>No. IAS 2 only permits specific identification, FIFO or weighted average cost (IAS 2, paragraph 25). LIFO is not allowed.</t>
-  </si>
-  <si>
-    <t>Which standard governs revenue from contracts with customers?</t>
-  </si>
-  <si>
-    <t>IFRS 15 Revenue from Contracts with Customers.</t>
-  </si>
-  <si>
-    <t>What are the five steps of the IFRS 15 revenue recognition model?</t>
-  </si>
-  <si>
-    <t>1) Identify the contract with the customer; 2) identify the performance obligations; 3) determine the transaction price; 4) allocate the transaction price to the performance obligations; 5) recognise revenue when (or as) a performance obligation is satisfied (IFRS 15).</t>
-  </si>
-  <si>
-    <t>What is a performance obligation under IFRS 15?</t>
-  </si>
-  <si>
-    <t>How is an item of property, plant and equipment initially measured under IAS 16?</t>
-  </si>
-  <si>
-    <t>An item of property, plant and equipment that qualifies for recognition as an asset shall be measured at its cost (IAS 16, paragraph 15).</t>
-  </si>
-  <si>
-    <t>What elements make up the cost of an item of property, plant and equipment under IAS 16?</t>
-  </si>
-  <si>
-    <t>Its purchase price including import duties and non-refundable taxes after discounts and rebates; costs directly attributable to bringing the asset to the location and condition necessary; and the initial estimate of dismantling, removal and site restoration costs (IAS 16, paragraph 16).</t>
-  </si>
-  <si>
-    <t>What are the two models for measuring property, plant and equipment after recognition under IAS 16?</t>
-  </si>
-  <si>
-    <t>The cost model (cost less accumulated depreciation and impairment losses) and the revaluation model (fair value at revaluation date less subsequent depreciation and impairment) (IAS 16, paragraphs 29-31).</t>
-  </si>
-  <si>
-    <t>What is depreciation according to IAS 16?</t>
-  </si>
-  <si>
-    <t>The systematic allocation of the depreciable amount of an asset over its useful life (IAS 16, paragraph 6).</t>
-  </si>
-  <si>
-    <t>When is an asset impaired under IAS 36?</t>
-  </si>
-  <si>
-    <t>An asset is impaired when its carrying amount exceeds its recoverable amount (IAS 36, paragraph 8).</t>
-  </si>
-  <si>
-    <t>What is the recoverable amount of an asset under IAS 36?</t>
-  </si>
-  <si>
-    <t>The higher of the asset's fair value less costs of disposal and its value in use (IAS 36, paragraph 6).</t>
-  </si>
-  <si>
-    <t>What is a cash-generating unit under IAS 36?</t>
-  </si>
-  <si>
-    <t>The smallest identifiable group of assets that generates cash inflows that are largely independent of the cash inflows from other assets or groups of assets (IAS 36, paragraph 6).</t>
-  </si>
-  <si>
-    <t>How does a lessee initially measure the lease liability under IFRS 16?</t>
-  </si>
-  <si>
-    <t>At the present value of the lease payments that are not paid at the commencement date, discounted using the interest rate implicit in the lease or, if not readily determinable, the lessee's incremental borrowing rate (IFRS 16, paragraph 26).</t>
-  </si>
-  <si>
-    <t>A promise in a contract with a customer to transfer to the customer a good or service (or bundle) that is distinct, or a series of distinct goods or services that are substantially the same (IFRS 15, paragraph 22).</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -477,139 +420,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="79" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>How are inventories measured under IAS 2?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>At the lower of cost and net realisable value (IAS 2, paragraph 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>What is net realisable value according to IAS 2?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The estimated selling price in the ordinary course of business less the estimated costs of completion and the estimated costs necessary to make the sale (IAS 2, paragraph 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Which cost formulas does IAS 2 allow for inventories?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Specific identification for items not ordinarily interchangeable; otherwise FIFO (first-in, first-out) or weighted average cost. The same formula must be used for all inventories of similar nature and use (IAS 2, paragraphs 23-25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Does IAS 2 permit the LIFO cost formula?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No. IAS 2 only permits specific identification, FIFO or weighted average cost (IAS 2, paragraph 25). LIFO is not allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Which standard governs revenue from contracts with customers?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IFRS 15 Revenue from Contracts with Customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>What are the five steps of the IFRS 15 revenue recognition model?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1) Identify the contract with the customer; 2) identify the performance obligations; 3) determine the transaction price; 4) allocate the transaction price to the performance obligations; 5) recognise revenue when (or as) a performance obligation is satisfied (IFRS 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>What is a performance obligation under IFRS 15?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A promise in a contract with a customer to transfer to the customer a good or service (or bundle) that is distinct, or a series of distinct goods or services that are substantially the same (IFRS 15, Appendix A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>How is an item of property, plant and equipment initially measured under IAS 16?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>An item of property, plant and equipment that qualifies for recognition as an asset shall be measured at its cost (IAS 16, paragraph 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>What elements make up the cost of an item of property, plant and equipment under IAS 16?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Its purchase price including import duties and non-refundable taxes after discounts and rebates; costs directly attributable to bringing the asset to the location and condition necessary; and the initial estimate of dismantling, removal and site restoration costs (IAS 16, paragraph 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>What are the two models for measuring property, plant and equipment after recognition under IAS 16?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The cost model (cost less accumulated depreciation and impairment losses) and the revaluation model (fair value at revaluation date less subsequent depreciation and impairment) (IAS 16, paragraphs 29-31).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>What is depreciation according to IAS 16?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The systematic allocation of the depreciable amount of an asset over its useful life (IAS 16, paragraph 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>When is an asset impaired under IAS 36?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>An asset is impaired when its carrying amount exceeds its recoverable amount (IAS 36, paragraph 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>What is the recoverable amount of an asset under IAS 36?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The higher of the asset's fair value less costs of disposal and its value in use (IAS 36, paragraph 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What is a cash-generating unit under IAS 36?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The smallest identifiable group of assets that generates cash inflows that are largely independent of the cash inflows from other assets or groups of assets (IAS 36, paragraph 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>How does a lessee initially measure the lease liability under IFRS 16?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>At the present value of the lease payments that are not paid at the commencement date, discounted using the interest rate implicit in the lease or, if not readily determinable, the lessee's incremental borrowing rate (IFRS 16, paragraph 26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A machine costs 120000 euros, has a residual value of 20000 euros and a useful life of 8 years. What is the annual straight-line depreciation, and which standard governs it?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Annual depreciation = (120000 - 20000) / 8 = 12500 euros per year, under IAS 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Inventory cost 50000 euros. Expected selling price is 52000 euros and costs to sell are 5000 euros. At what amount is the inventory measured under IAS 2?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Net realisable value = 52000 - 5000 = 47000 euros, which is below cost, so the inventory is measured at 47000 euros (write-down of 3000 euros) under IAS 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>An asset has a carrying amount of 200000 euros, fair value less costs of disposal of 150000 euros and value in use of 170000 euros. What is the impairment loss under IAS 36?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Recoverable amount = higher of 150000 and 170000 = 170000 euros. Impairment loss = 200000 - 170000 = 30000 euros (IAS 36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A lease has 5 annual payments of 10000 euros payable in arrears and the discount rate is 5 percent. What is the initial lease liability under IFRS 16?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The present value of an annuity of 10000 for 5 years at 5% is approximately 43295 euros, recognised as the initial lease liability under IFRS 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A contract has a total price of 100000 euros covering two performance obligations with stand-alone selling prices of 40000 and 80000 euros. How is the transaction price allocated under IFRS 15?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>On a relative stand-alone selling price basis: 100000 x 40000/120000 = 33333 euros to the first obligation and 100000 x 80000/120000 = 66667 euros to the second (IFRS 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Equipment costs 250000 euros with a residual value of 10000 euros and a useful life of 6 years. What is the annual straight-line depreciation?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>(250000 - 10000) / 6 = 40000 euros per year (IAS 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A machine cost 90000 euros, residual value zero, total expected production 300000 units. This year it produced 45000 units. What is the depreciation charge under the units of production method?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90000 x 45000/300000 = 13500 euros (IAS 16, units of production method).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A building has a carrying amount of 500000 euros. Its value in use is 460000 euros and its fair value less costs of disposal is 430000 euros. Is it impaired, and by how much?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Recoverable amount = 460000 euros (higher of the two). Impairment loss = 500000 - 460000 = 40000 euros (IAS 36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Which standard applies to a retailer's merchandise held for resale?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IAS 2 Inventories: merchandise purchased by a retailer and held for resale is inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A company signs a 10-year office lease. As lessee, what must it recognise at commencement and under which standard?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Under IFRS 16 the lessee recognises a right-of-use asset and a lease liability at the commencement date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Under which standard is goodwill tested for impairment, and how often?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IAS 36: goodwill acquired in a business combination is tested for impairment annually, and whenever there is an indication of impairment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>When is revenue recognised over time rather than at a point in time under IFRS 15?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>When one of the IFRS 15 paragraph 35 criteria is met: the customer simultaneously receives and consumes the benefits; the entity's performance creates or enhances an asset the customer controls; or the asset has no alternative use and the entity has an enforceable right to payment for performance completed to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>What does IFRS 9 say about expected credit losses?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Out of scope: IFRS 9 is not in this assistant's knowledge base, which covers only IAS 2, IAS 16, IAS 36, IFRS 15 and IFRS 16. The assistant should say it cannot answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>How should deferred tax assets be recognised?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Out of scope: deferred tax is governed by IAS 12, which is not in the knowledge base. The assistant should say it cannot answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>What is the current VAT rate in Italy?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Out of scope: VAT rates are not part of IFRS standards. The assistant should refuse and explain it only answers IFRS/IAS questions.</t>
+        </is>
       </c>
     </row>
   </sheetData>
